--- a/tools/importer/reports/import-section-landing.report.xlsx
+++ b/tools/importer/reports/import-section-landing.report.xlsx
@@ -52,7 +52,7 @@
     <t>section-landing</t>
   </si>
   <si>
-    <t>2026-04-24T21:23:19.724Z</t>
+    <t>2026-04-24T23:00:27.473Z</t>
   </si>
   <si>
     <t>WorkSafeNB | Employers</t>
@@ -70,7 +70,7 @@
     <t>health-care</t>
   </si>
   <si>
-    <t>2026-04-24T21:23:10.819Z</t>
+    <t>2026-04-24T23:00:17.452Z</t>
   </si>
   <si>
     <t>WorkSafeNB | Health Care</t>
@@ -91,7 +91,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-04-23T19:57:10.589Z</t>
+    <t>2026-04-24T22:14:37.492Z</t>
   </si>
   <si>
     <t>WorkSafeNB | WorkSafeNB</t>
@@ -109,7 +109,7 @@
     <t>policy-and-legal</t>
   </si>
   <si>
-    <t>2026-04-24T21:23:24.285Z</t>
+    <t>2026-04-24T23:00:32.246Z</t>
   </si>
   <si>
     <t>WorkSafeNB | Policy and Legal</t>
@@ -127,7 +127,7 @@
     <t>workers</t>
   </si>
   <si>
-    <t>2026-04-24T21:23:15.360Z</t>
+    <t>2026-04-24T23:00:22.071Z</t>
   </si>
   <si>
     <t>WorkSafeNB | Workers</t>
